--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1481</v>
+        <v>1312</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-401</v>
+        <v>-232</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -587,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-306</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1481</v>
+        <v>1312</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-401</v>
+        <v>-232</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -610,7 +601,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1481</v>
+        <v>1312</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-401</v>
+        <v>-232</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -655,7 +646,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -681,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>650</v>
+        <v>745</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>880</v>
+        <v>978</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-230</v>
+        <v>-233</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,7 +689,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -712,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>731</v>
+        <v>978</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-231</v>
+        <v>-233</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,7 +734,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -767,17 +758,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>731</v>
+        <v>802</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-231</v>
+        <v>-302</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,7 +779,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -812,17 +803,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>500</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>731</v>
+        <v>802</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-231</v>
+        <v>-302</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,7 +824,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -847,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +848,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>802</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-252</v>
+        <v>-302</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,147 +869,12 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-316</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>802</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-202</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>802</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-202</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>666</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-216</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -613,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1080</v>
+        <v>350</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1312</v>
+        <v>978</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-232</v>
+        <v>-628</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -644,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -668,7 +686,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-206</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -703,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-106</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>978</v>
+        <v>731</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-233</v>
+        <v>-231</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -758,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>802</v>
+        <v>731</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-302</v>
+        <v>-231</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -803,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>500</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>802</v>
+        <v>731</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-302</v>
+        <v>-231</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>802</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-302</v>
+        <v>-202</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -875,6 +893,1131 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-316</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-202</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-202</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-546</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>28-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-552</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>01-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-78</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-546</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-106</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-78</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-116</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-106</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-853</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>824</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-739</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-613</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-116</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-106</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>521</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1042</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>635</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-928</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-913</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -555,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1080</v>
+        <v>500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1312</v>
+        <v>731</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-232</v>
+        <v>-231</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1080</v>
+        <v>500</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1312</v>
+        <v>731</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-232</v>
+        <v>-231</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>978</v>
+        <v>731</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-628</v>
+        <v>-231</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>745</v>
+        <v>600</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>978</v>
+        <v>802</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-233</v>
+        <v>-202</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>731</v>
+        <v>802</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-231</v>
+        <v>-202</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>731</v>
+        <v>802</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-231</v>
+        <v>-202</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Air Arabia Egypt E5-592</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>500</v>
+        <v>1017</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>731</v>
+        <v>1563</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-231</v>
+        <v>-546</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>600</v>
+        <v>1250</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>802</v>
+        <v>1563</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-202</v>
+        <v>-313</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>600</v>
+        <v>1250</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>802</v>
+        <v>1563</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-202</v>
+        <v>-313</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Air Arabia Egypt E5-592</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>600</v>
+        <v>1011</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>802</v>
+        <v>1563</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-202</v>
+        <v>-552</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,26 +992,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1017</v>
+        <v>1250</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-546</v>
+        <v>-313</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1037,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>EgyptAir MS-634</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1250</v>
+        <v>1485</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-313</v>
+        <v>-78</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,7 +1082,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,28 +1127,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1011</v>
+        <v>1080</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-552</v>
+        <v>-483</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,7 +1172,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1217,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1485</v>
+        <v>1250</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-78</v>
+        <v>-313</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1253,771 +1244,6 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>05-JUL-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1017</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-546</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>05-JUL-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-313</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-313</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-78</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-313</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-313</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>710</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-853</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>824</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-739</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-613</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>521</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-1042</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>635</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-928</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>650</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-913</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>731</v>
+        <v>1312</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-231</v>
+        <v>-362</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>731</v>
+        <v>1312</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-231</v>
+        <v>-362</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>500</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>731</v>
+        <v>1312</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-231</v>
+        <v>-232</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>802</v>
+        <v>731</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-202</v>
+        <v>-231</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>802</v>
+        <v>731</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-202</v>
+        <v>-231</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>802</v>
+        <v>731</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-202</v>
+        <v>-231</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1017</v>
+        <v>600</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1563</v>
+        <v>802</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-546</v>
+        <v>-202</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1563</v>
+        <v>802</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-313</v>
+        <v>-202</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -906,13 +915,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1563</v>
+        <v>802</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-313</v>
+        <v>-202</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-552</v>
+        <v>-546</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>20</v>
@@ -968,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>28-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1485</v>
+        <v>1250</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-78</v>
+        <v>-313</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Air Arabia Egypt E5-592</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1250</v>
+        <v>1011</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-313</v>
+        <v>-552</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-483</v>
+        <v>-313</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1148,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>EgyptAir MS-634</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1250</v>
+        <v>1485</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-313</v>
+        <v>-78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1207,43 +1216,763 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-546</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-313</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-552</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-78</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>12-JUL-26</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>830</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-733</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-116</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="E24" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>-313</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-763</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>824</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-739</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-613</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-1036</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-143</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>19-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-116</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-483</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-634</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>635</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-928</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-141</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-913</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-436</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-592</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>811</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-752</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>950</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1312</v>
+        <v>1481</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-362</v>
+        <v>-531</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>950</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1312</v>
+        <v>1481</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-362</v>
+        <v>-531</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -648,10 +648,10 @@
         <v>1080</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1312</v>
+        <v>1481</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-232</v>
+        <v>-401</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-546</v>
+        <v>-552</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>20</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1022,7 +1022,7 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>EgyptAir MS-634</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1250</v>
+        <v>1485</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-313</v>
+        <v>-78</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-552</v>
+        <v>-546</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>20</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1157,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Air Arabia Egypt E5-592</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1485</v>
+        <v>1011</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-78</v>
+        <v>-552</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1017</v>
+        <v>1080</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-546</v>
+        <v>-483</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>EgyptAir MS-634</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1250</v>
+        <v>1485</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-313</v>
+        <v>-78</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1011</v>
+        <v>830</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-552</v>
+        <v>-733</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>20</v>
@@ -1337,7 +1337,7 @@
       <c r="I19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1382,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,28 +1406,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-116</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1485</v>
+        <v>1250</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-78</v>
+        <v>-313</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>830</v>
+        <v>527</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-733</v>
+        <v>-1036</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>20</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>19-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-313</v>
+        <v>-483</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1564,415 +1564,10 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-763</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>824</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-739</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-613</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>527</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-1036</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>635</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-928</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>650</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-913</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>22-JUL-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>811</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-752</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>950</v>
+        <v>1080</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1481</v>
+        <v>1563</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-531</v>
+        <v>-483</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>950</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1481</v>
+        <v>1563</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-531</v>
+        <v>-483</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1481</v>
+        <v>1563</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-401</v>
+        <v>-483</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>731</v>
+        <v>1563</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-231</v>
+        <v>-613</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -709,7 +700,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Air Arabia Egypt E5-592</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>500</v>
+        <v>1012</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>731</v>
+        <v>1563</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-231</v>
+        <v>-551</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>500</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>731</v>
+        <v>1563</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-231</v>
+        <v>-483</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +812,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-141</t>
+          <t>Air Arabia Egypt E5-592</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>600</v>
+        <v>831</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>802</v>
+        <v>1563</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-202</v>
+        <v>-732</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-316</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>802</v>
+        <v>1563</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-202</v>
+        <v>-483</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -915,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>600</v>
+        <v>1080</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>802</v>
+        <v>1563</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-202</v>
+        <v>-483</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>EgyptAir MS-634</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1011</v>
+        <v>947</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-552</v>
+        <v>-616</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1250</v>
+        <v>950</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-313</v>
+        <v>-613</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1024,7 +1015,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,528 +1037,33 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-634</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1485</v>
+        <v>950</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1563</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-78</v>
+        <v>-613</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>05-JUL-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>1017</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-546</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>05-JUL-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-313</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1011</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-552</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>08-JUL-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>1485</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-78</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>830</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-733</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-313</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-592</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>527</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-1036</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>19-JUL-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_ELQ_HMB_threats.xlsx
+++ b/excel_routes/route_ELQ_HMB_threats.xlsx
@@ -54,8 +54,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-143</t>
+          <t>Nesma Airlines NE-141</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1080</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1563</v>
+        <v>666</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-483</v>
+        <v>-266</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-116</t>
+          <t>Nile Air NP-316</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1080</v>
+        <v>401</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1563</v>
+        <v>666</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-483</v>
+        <v>-265</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -636,26 +636,26 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1080</v>
+        <v>500</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1563</v>
+        <v>666</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-483</v>
+        <v>-166</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,26 +681,26 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>950</v>
+        <v>400</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1563</v>
+        <v>510</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-613</v>
+        <v>-110</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1012</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1563</v>
+        <v>510</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-551</v>
+        <v>-109</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-106</t>
+          <t>Nesma Airlines NE-143</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1080</v>
+        <v>500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1563</v>
+        <v>562</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-483</v>
+        <v>-62</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,258 +812,33 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-592</t>
+          <t>Nile Air NP-106</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>831</v>
+        <v>500</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1563</v>
+        <v>562</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-732</v>
+        <v>-62</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-143</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-116</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-483</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-634</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>947</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-616</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-141</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-613</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15-JUL-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-436</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-106</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-613</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
